--- a/Program/docs/TIAProjectTexts_es_filled.xlsx
+++ b/Program/docs/TIAProjectTexts_es_filled.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2774">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2779">
   <x:si>
     <x:t xml:space="preserve">Category</x:t>
   </x:si>
@@ -8120,6 +8120,9 @@
     <x:t xml:space="preserve">Aplicar</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Anular husillo</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Anular bloqueo de herramienta</x:t>
   </x:si>
   <x:si>
@@ -8162,6 +8165,9 @@
     <x:t xml:space="preserve">Numero de herramienta invalido</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Última duración:</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">M40 P1 = Extender soporte trasero</x:t>
   </x:si>
   <x:si>
@@ -8261,6 +8267,9 @@
     <x:t xml:space="preserve">Pantalla inicial</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">PASO</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Eje herramienta: fallo de referenciado</x:t>
   </x:si>
   <x:si>
@@ -8277,6 +8286,12 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Tiempo de rotacion herramienta excedido</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ID ranura herramienta 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ID ranura herramienta 2</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">ID ranura herramienta 3</x:t>
@@ -14800,7 +14815,7 @@
         <x:v>624</x:v>
       </x:c>
       <x:c r="G277" s="0" t="s">
-        <x:v>809</x:v>
+        <x:v>2703</x:v>
       </x:c>
     </x:row>
     <x:row r="278">
@@ -14823,7 +14838,7 @@
         <x:v>627</x:v>
       </x:c>
       <x:c r="G278" s="0" t="s">
-        <x:v>2703</x:v>
+        <x:v>2704</x:v>
       </x:c>
     </x:row>
     <x:row r="279">
@@ -14846,7 +14861,7 @@
         <x:v>627</x:v>
       </x:c>
       <x:c r="G279" s="0" t="s">
-        <x:v>2703</x:v>
+        <x:v>2704</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
@@ -15076,7 +15091,7 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="G289" s="0" t="s">
-        <x:v>2704</x:v>
+        <x:v>2705</x:v>
       </x:c>
     </x:row>
     <x:row r="290">
@@ -15099,7 +15114,7 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="G290" s="0" t="s">
-        <x:v>2704</x:v>
+        <x:v>2705</x:v>
       </x:c>
     </x:row>
     <x:row r="291">
@@ -15122,7 +15137,7 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="G291" s="0" t="s">
-        <x:v>2704</x:v>
+        <x:v>2705</x:v>
       </x:c>
     </x:row>
     <x:row r="292">
@@ -15467,7 +15482,7 @@
         <x:v>699</x:v>
       </x:c>
       <x:c r="G306" s="0" t="s">
-        <x:v>2705</x:v>
+        <x:v>2706</x:v>
       </x:c>
     </x:row>
     <x:row r="307">
@@ -15490,7 +15505,7 @@
         <x:v>699</x:v>
       </x:c>
       <x:c r="G307" s="0" t="s">
-        <x:v>2705</x:v>
+        <x:v>2706</x:v>
       </x:c>
     </x:row>
     <x:row r="308">
@@ -15513,7 +15528,7 @@
         <x:v>699</x:v>
       </x:c>
       <x:c r="G308" s="0" t="s">
-        <x:v>2705</x:v>
+        <x:v>2706</x:v>
       </x:c>
     </x:row>
     <x:row r="309">
@@ -15743,7 +15758,7 @@
         <x:v>725</x:v>
       </x:c>
       <x:c r="G318" s="0" t="s">
-        <x:v>2706</x:v>
+        <x:v>2707</x:v>
       </x:c>
     </x:row>
     <x:row r="319">
@@ -16433,7 +16448,7 @@
         <x:v>789</x:v>
       </x:c>
       <x:c r="G348" s="0" t="s">
-        <x:v>2707</x:v>
+        <x:v>2708</x:v>
       </x:c>
     </x:row>
     <x:row r="349">
@@ -16456,7 +16471,7 @@
         <x:v>792</x:v>
       </x:c>
       <x:c r="G349" s="0" t="s">
-        <x:v>2708</x:v>
+        <x:v>2709</x:v>
       </x:c>
     </x:row>
     <x:row r="350">
@@ -16732,7 +16747,7 @@
         <x:v>825</x:v>
       </x:c>
       <x:c r="G361" s="0" t="s">
-        <x:v>2709</x:v>
+        <x:v>2710</x:v>
       </x:c>
     </x:row>
     <x:row r="362">
@@ -17008,7 +17023,7 @@
         <x:v>852</x:v>
       </x:c>
       <x:c r="G373" s="0" t="s">
-        <x:v>2710</x:v>
+        <x:v>2711</x:v>
       </x:c>
     </x:row>
     <x:row r="374">
@@ -17031,7 +17046,7 @@
         <x:v>855</x:v>
       </x:c>
       <x:c r="G374" s="0" t="s">
-        <x:v>2711</x:v>
+        <x:v>2712</x:v>
       </x:c>
     </x:row>
     <x:row r="375">
@@ -17997,7 +18012,7 @@
         <x:v>948</x:v>
       </x:c>
       <x:c r="G416" s="0" t="s">
-        <x:v>2712</x:v>
+        <x:v>2713</x:v>
       </x:c>
     </x:row>
     <x:row r="417">
@@ -18020,7 +18035,7 @@
         <x:v>948</x:v>
       </x:c>
       <x:c r="G417" s="0" t="s">
-        <x:v>2712</x:v>
+        <x:v>2713</x:v>
       </x:c>
     </x:row>
     <x:row r="418">
@@ -18043,7 +18058,7 @@
         <x:v>948</x:v>
       </x:c>
       <x:c r="G418" s="0" t="s">
-        <x:v>2712</x:v>
+        <x:v>2713</x:v>
       </x:c>
     </x:row>
     <x:row r="419">
@@ -18066,7 +18081,7 @@
         <x:v>948</x:v>
       </x:c>
       <x:c r="G419" s="0" t="s">
-        <x:v>2712</x:v>
+        <x:v>2713</x:v>
       </x:c>
     </x:row>
     <x:row r="420">
@@ -18089,7 +18104,7 @@
         <x:v>948</x:v>
       </x:c>
       <x:c r="G420" s="0" t="s">
-        <x:v>2712</x:v>
+        <x:v>2713</x:v>
       </x:c>
     </x:row>
     <x:row r="421">
@@ -18112,7 +18127,7 @@
         <x:v>948</x:v>
       </x:c>
       <x:c r="G421" s="0" t="s">
-        <x:v>2712</x:v>
+        <x:v>2713</x:v>
       </x:c>
     </x:row>
     <x:row r="422">
@@ -18181,7 +18196,7 @@
         <x:v>966</x:v>
       </x:c>
       <x:c r="G424" s="0" t="s">
-        <x:v>2713</x:v>
+        <x:v>2714</x:v>
       </x:c>
     </x:row>
     <x:row r="425">
@@ -18204,7 +18219,7 @@
         <x:v>969</x:v>
       </x:c>
       <x:c r="G425" s="0" t="s">
-        <x:v>2714</x:v>
+        <x:v>2715</x:v>
       </x:c>
     </x:row>
     <x:row r="426">
@@ -18227,7 +18242,7 @@
         <x:v>969</x:v>
       </x:c>
       <x:c r="G426" s="0" t="s">
-        <x:v>2714</x:v>
+        <x:v>2715</x:v>
       </x:c>
     </x:row>
     <x:row r="427">
@@ -18411,7 +18426,7 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="G434" s="0" t="s">
-        <x:v>2715</x:v>
+        <x:v>2716</x:v>
       </x:c>
     </x:row>
     <x:row r="435">
@@ -19722,7 +19737,7 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="G491" s="0" t="s">
-        <x:v>2716</x:v>
+        <x:v>2717</x:v>
       </x:c>
     </x:row>
     <x:row r="492">
@@ -20182,7 +20197,7 @@
         <x:v>1171</x:v>
       </x:c>
       <x:c r="G511" s="0" t="s">
-        <x:v>795</x:v>
+        <x:v>2718</x:v>
       </x:c>
     </x:row>
     <x:row r="512">
@@ -20481,7 +20496,7 @@
         <x:v>1213</x:v>
       </x:c>
       <x:c r="G524" s="0" t="s">
-        <x:v>2717</x:v>
+        <x:v>2719</x:v>
       </x:c>
     </x:row>
     <x:row r="525">
@@ -20527,7 +20542,7 @@
         <x:v>1219</x:v>
       </x:c>
       <x:c r="G526" s="0" t="s">
-        <x:v>2718</x:v>
+        <x:v>2720</x:v>
       </x:c>
     </x:row>
     <x:row r="527">
@@ -20550,7 +20565,7 @@
         <x:v>1222</x:v>
       </x:c>
       <x:c r="G527" s="0" t="s">
-        <x:v>2719</x:v>
+        <x:v>2721</x:v>
       </x:c>
     </x:row>
     <x:row r="528">
@@ -20573,7 +20588,7 @@
         <x:v>1225</x:v>
       </x:c>
       <x:c r="G528" s="0" t="s">
-        <x:v>2720</x:v>
+        <x:v>2722</x:v>
       </x:c>
     </x:row>
     <x:row r="529">
@@ -21608,7 +21623,7 @@
         <x:v>1325</x:v>
       </x:c>
       <x:c r="G573" s="0" t="s">
-        <x:v>2721</x:v>
+        <x:v>2723</x:v>
       </x:c>
     </x:row>
     <x:row r="574">
@@ -21838,7 +21853,7 @@
         <x:v>1347</x:v>
       </x:c>
       <x:c r="G583" s="0" t="s">
-        <x:v>2722</x:v>
+        <x:v>2724</x:v>
       </x:c>
     </x:row>
     <x:row r="584">
@@ -21976,7 +21991,7 @@
         <x:v>1362</x:v>
       </x:c>
       <x:c r="G589" s="0" t="s">
-        <x:v>2723</x:v>
+        <x:v>2725</x:v>
       </x:c>
     </x:row>
     <x:row r="590">
@@ -22045,7 +22060,7 @@
         <x:v>1371</x:v>
       </x:c>
       <x:c r="G592" s="0" t="s">
-        <x:v>2724</x:v>
+        <x:v>2726</x:v>
       </x:c>
     </x:row>
     <x:row r="593">
@@ -22298,7 +22313,7 @@
         <x:v>1398</x:v>
       </x:c>
       <x:c r="G603" s="0" t="s">
-        <x:v>2725</x:v>
+        <x:v>2727</x:v>
       </x:c>
     </x:row>
     <x:row r="604">
@@ -22367,7 +22382,7 @@
         <x:v>1406</x:v>
       </x:c>
       <x:c r="G606" s="0" t="s">
-        <x:v>2726</x:v>
+        <x:v>2728</x:v>
       </x:c>
     </x:row>
     <x:row r="607">
@@ -22390,7 +22405,7 @@
         <x:v>1409</x:v>
       </x:c>
       <x:c r="G607" s="0" t="s">
-        <x:v>2727</x:v>
+        <x:v>2729</x:v>
       </x:c>
     </x:row>
     <x:row r="608">
@@ -22413,7 +22428,7 @@
         <x:v>1412</x:v>
       </x:c>
       <x:c r="G608" s="0" t="s">
-        <x:v>2728</x:v>
+        <x:v>2730</x:v>
       </x:c>
     </x:row>
     <x:row r="609">
@@ -22919,7 +22934,7 @@
         <x:v>1467</x:v>
       </x:c>
       <x:c r="G630" s="0" t="s">
-        <x:v>2729</x:v>
+        <x:v>2731</x:v>
       </x:c>
     </x:row>
     <x:row r="631">
@@ -22942,7 +22957,7 @@
         <x:v>1467</x:v>
       </x:c>
       <x:c r="G631" s="0" t="s">
-        <x:v>2729</x:v>
+        <x:v>2731</x:v>
       </x:c>
     </x:row>
     <x:row r="632">
@@ -22965,7 +22980,7 @@
         <x:v>1467</x:v>
       </x:c>
       <x:c r="G632" s="0" t="s">
-        <x:v>2729</x:v>
+        <x:v>2731</x:v>
       </x:c>
     </x:row>
     <x:row r="633">
@@ -22988,7 +23003,7 @@
         <x:v>1467</x:v>
       </x:c>
       <x:c r="G633" s="0" t="s">
-        <x:v>2729</x:v>
+        <x:v>2731</x:v>
       </x:c>
     </x:row>
     <x:row r="634">
@@ -23011,7 +23026,7 @@
         <x:v>1467</x:v>
       </x:c>
       <x:c r="G634" s="0" t="s">
-        <x:v>2729</x:v>
+        <x:v>2731</x:v>
       </x:c>
     </x:row>
     <x:row r="635">
@@ -23034,7 +23049,7 @@
         <x:v>1467</x:v>
       </x:c>
       <x:c r="G635" s="0" t="s">
-        <x:v>2729</x:v>
+        <x:v>2731</x:v>
       </x:c>
     </x:row>
     <x:row r="636">
@@ -23057,7 +23072,7 @@
         <x:v>1467</x:v>
       </x:c>
       <x:c r="G636" s="0" t="s">
-        <x:v>2729</x:v>
+        <x:v>2731</x:v>
       </x:c>
     </x:row>
     <x:row r="637">
@@ -23080,7 +23095,7 @@
         <x:v>1467</x:v>
       </x:c>
       <x:c r="G637" s="0" t="s">
-        <x:v>2729</x:v>
+        <x:v>2731</x:v>
       </x:c>
     </x:row>
     <x:row r="638">
@@ -23103,7 +23118,7 @@
         <x:v>1467</x:v>
       </x:c>
       <x:c r="G638" s="0" t="s">
-        <x:v>2729</x:v>
+        <x:v>2731</x:v>
       </x:c>
     </x:row>
     <x:row r="639">
@@ -23149,7 +23164,7 @@
         <x:v>1489</x:v>
       </x:c>
       <x:c r="G640" s="0" t="s">
-        <x:v>2730</x:v>
+        <x:v>2732</x:v>
       </x:c>
     </x:row>
     <x:row r="641">
@@ -25081,7 +25096,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G724" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="725">
@@ -25104,7 +25119,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G725" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="726">
@@ -25127,7 +25142,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G726" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="727">
@@ -25150,7 +25165,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G727" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="728">
@@ -25173,7 +25188,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G728" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="729">
@@ -25196,7 +25211,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G729" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="730">
@@ -25219,7 +25234,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G730" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="731">
@@ -25242,7 +25257,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G731" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="732">
@@ -25265,7 +25280,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G732" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="733">
@@ -25288,7 +25303,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G733" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="734">
@@ -25311,7 +25326,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G734" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="735">
@@ -25334,7 +25349,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G735" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="736">
@@ -25357,7 +25372,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G736" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="737">
@@ -25380,7 +25395,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G737" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="738">
@@ -25403,7 +25418,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G738" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="739">
@@ -25426,7 +25441,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G739" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="740">
@@ -25449,7 +25464,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G740" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="741">
@@ -25472,7 +25487,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G741" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="742">
@@ -25495,7 +25510,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G742" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="743">
@@ -25518,7 +25533,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G743" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="744">
@@ -25541,7 +25556,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G744" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="745">
@@ -25564,7 +25579,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G745" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="746">
@@ -25587,7 +25602,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G746" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="747">
@@ -25610,7 +25625,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G747" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="748">
@@ -25633,7 +25648,7 @@
         <x:v>1672</x:v>
       </x:c>
       <x:c r="G748" s="0" t="s">
-        <x:v>2731</x:v>
+        <x:v>2733</x:v>
       </x:c>
     </x:row>
     <x:row r="749">
@@ -25679,7 +25694,7 @@
         <x:v>1726</x:v>
       </x:c>
       <x:c r="G750" s="0" t="s">
-        <x:v>2732</x:v>
+        <x:v>2734</x:v>
       </x:c>
     </x:row>
     <x:row r="751">
@@ -25702,7 +25717,7 @@
         <x:v>1729</x:v>
       </x:c>
       <x:c r="G751" s="0" t="s">
-        <x:v>2733</x:v>
+        <x:v>2735</x:v>
       </x:c>
     </x:row>
     <x:row r="752">
@@ -25725,7 +25740,7 @@
         <x:v>1732</x:v>
       </x:c>
       <x:c r="G752" s="0" t="s">
-        <x:v>2734</x:v>
+        <x:v>2736</x:v>
       </x:c>
     </x:row>
     <x:row r="753">
@@ -25748,7 +25763,7 @@
         <x:v>1735</x:v>
       </x:c>
       <x:c r="G753" s="0" t="s">
-        <x:v>2735</x:v>
+        <x:v>2737</x:v>
       </x:c>
     </x:row>
     <x:row r="754">
@@ -25771,7 +25786,7 @@
         <x:v>1738</x:v>
       </x:c>
       <x:c r="G754" s="0" t="s">
-        <x:v>2736</x:v>
+        <x:v>2738</x:v>
       </x:c>
     </x:row>
     <x:row r="755">
@@ -25794,7 +25809,7 @@
         <x:v>1741</x:v>
       </x:c>
       <x:c r="G755" s="0" t="s">
-        <x:v>2737</x:v>
+        <x:v>2739</x:v>
       </x:c>
     </x:row>
     <x:row r="756">
@@ -25817,7 +25832,7 @@
         <x:v>1744</x:v>
       </x:c>
       <x:c r="G756" s="0" t="s">
-        <x:v>2738</x:v>
+        <x:v>2740</x:v>
       </x:c>
     </x:row>
     <x:row r="757">
@@ -25932,7 +25947,7 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="G761" s="0" t="s">
-        <x:v>2739</x:v>
+        <x:v>2741</x:v>
       </x:c>
     </x:row>
     <x:row r="762">
@@ -25955,7 +25970,7 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="G762" s="0" t="s">
-        <x:v>2739</x:v>
+        <x:v>2741</x:v>
       </x:c>
     </x:row>
     <x:row r="763">
@@ -25978,7 +25993,7 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="G763" s="0" t="s">
-        <x:v>2739</x:v>
+        <x:v>2741</x:v>
       </x:c>
     </x:row>
     <x:row r="764">
@@ -26001,7 +26016,7 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="G764" s="0" t="s">
-        <x:v>2739</x:v>
+        <x:v>2741</x:v>
       </x:c>
     </x:row>
     <x:row r="765">
@@ -26024,7 +26039,7 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="G765" s="0" t="s">
-        <x:v>2739</x:v>
+        <x:v>2741</x:v>
       </x:c>
     </x:row>
     <x:row r="766">
@@ -26047,7 +26062,7 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="G766" s="0" t="s">
-        <x:v>2739</x:v>
+        <x:v>2741</x:v>
       </x:c>
     </x:row>
     <x:row r="767">
@@ -26070,7 +26085,7 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="G767" s="0" t="s">
-        <x:v>2739</x:v>
+        <x:v>2741</x:v>
       </x:c>
     </x:row>
     <x:row r="768">
@@ -26438,7 +26453,7 @@
         <x:v>1815</x:v>
       </x:c>
       <x:c r="G783" s="0" t="s">
-        <x:v>2740</x:v>
+        <x:v>2742</x:v>
       </x:c>
     </x:row>
     <x:row r="784">
@@ -26461,7 +26476,7 @@
         <x:v>1818</x:v>
       </x:c>
       <x:c r="G784" s="0" t="s">
-        <x:v>2741</x:v>
+        <x:v>2743</x:v>
       </x:c>
     </x:row>
     <x:row r="785">
@@ -26622,7 +26637,7 @@
         <x:v>1839</x:v>
       </x:c>
       <x:c r="G791" s="0" t="s">
-        <x:v>2742</x:v>
+        <x:v>2744</x:v>
       </x:c>
     </x:row>
     <x:row r="792">
@@ -26714,7 +26729,7 @@
         <x:v>1850</x:v>
       </x:c>
       <x:c r="G795" s="0" t="s">
-        <x:v>2743</x:v>
+        <x:v>2745</x:v>
       </x:c>
     </x:row>
     <x:row r="796">
@@ -26737,7 +26752,7 @@
         <x:v>1853</x:v>
       </x:c>
       <x:c r="G796" s="0" t="s">
-        <x:v>2744</x:v>
+        <x:v>2746</x:v>
       </x:c>
     </x:row>
     <x:row r="797">
@@ -26875,7 +26890,7 @@
         <x:v>1872</x:v>
       </x:c>
       <x:c r="G802" s="0" t="s">
-        <x:v>2745</x:v>
+        <x:v>2747</x:v>
       </x:c>
     </x:row>
     <x:row r="803">
@@ -26898,7 +26913,7 @@
         <x:v>1875</x:v>
       </x:c>
       <x:c r="G803" s="0" t="s">
-        <x:v>2746</x:v>
+        <x:v>2748</x:v>
       </x:c>
     </x:row>
     <x:row r="804">
@@ -26921,7 +26936,7 @@
         <x:v>1878</x:v>
       </x:c>
       <x:c r="G804" s="0" t="s">
-        <x:v>2747</x:v>
+        <x:v>2749</x:v>
       </x:c>
     </x:row>
     <x:row r="805">
@@ -26944,7 +26959,7 @@
         <x:v>1881</x:v>
       </x:c>
       <x:c r="G805" s="0" t="s">
-        <x:v>2748</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="806">
@@ -27036,7 +27051,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G809" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="810">
@@ -27059,7 +27074,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G810" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="811">
@@ -27082,7 +27097,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G811" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="812">
@@ -27105,7 +27120,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G812" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="813">
@@ -27128,7 +27143,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G813" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="814">
@@ -27151,7 +27166,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G814" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="815">
@@ -27174,7 +27189,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G815" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="816">
@@ -27197,7 +27212,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G816" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="817">
@@ -27220,7 +27235,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G817" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="818">
@@ -27243,7 +27258,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G818" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="819">
@@ -27266,7 +27281,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G819" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="820">
@@ -27289,7 +27304,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G820" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="821">
@@ -27312,7 +27327,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G821" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="822">
@@ -27335,7 +27350,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G822" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="823">
@@ -27358,7 +27373,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G823" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="824">
@@ -27381,7 +27396,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G824" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="825">
@@ -27404,7 +27419,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G825" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="826">
@@ -27427,7 +27442,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G826" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="827">
@@ -27450,7 +27465,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G827" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="828">
@@ -27473,7 +27488,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G828" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="829">
@@ -27496,7 +27511,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G829" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="830">
@@ -27519,7 +27534,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G830" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="831">
@@ -27542,7 +27557,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G831" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="832">
@@ -27565,7 +27580,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G832" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="833">
@@ -27588,7 +27603,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G833" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="834">
@@ -27611,7 +27626,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G834" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="835">
@@ -27634,7 +27649,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G835" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="836">
@@ -27657,7 +27672,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G836" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="837">
@@ -27680,7 +27695,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G837" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="838">
@@ -27703,7 +27718,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G838" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="839">
@@ -27726,7 +27741,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G839" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="840">
@@ -27749,7 +27764,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G840" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="841">
@@ -27772,7 +27787,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G841" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="842">
@@ -27795,7 +27810,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G842" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="843">
@@ -27818,7 +27833,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G843" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="844">
@@ -27841,7 +27856,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G844" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="845">
@@ -27864,7 +27879,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G845" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="846">
@@ -27887,7 +27902,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G846" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="847">
@@ -27910,7 +27925,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G847" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="848">
@@ -27933,7 +27948,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G848" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="849">
@@ -27956,7 +27971,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G849" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="850">
@@ -27979,7 +27994,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G850" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="851">
@@ -28002,7 +28017,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G851" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="852">
@@ -28025,7 +28040,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G852" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="853">
@@ -28048,7 +28063,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G853" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="854">
@@ -28071,7 +28086,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G854" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="855">
@@ -28094,7 +28109,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G855" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="856">
@@ -28117,7 +28132,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G856" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="857">
@@ -28140,7 +28155,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G857" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="858">
@@ -28163,7 +28178,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G858" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="859">
@@ -28186,7 +28201,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G859" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="860">
@@ -28209,7 +28224,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G860" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="861">
@@ -28232,7 +28247,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G861" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="862">
@@ -28255,7 +28270,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G862" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="863">
@@ -28278,7 +28293,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G863" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="864">
@@ -28301,7 +28316,7 @@
         <x:v>1892</x:v>
       </x:c>
       <x:c r="G864" s="0" t="s">
-        <x:v>2749</x:v>
+        <x:v>2751</x:v>
       </x:c>
     </x:row>
     <x:row r="865">
@@ -28416,7 +28431,7 @@
         <x:v>2016</x:v>
       </x:c>
       <x:c r="G869" s="0" t="s">
-        <x:v>1672</x:v>
+        <x:v>2752</x:v>
       </x:c>
     </x:row>
     <x:row r="870">
@@ -28439,7 +28454,7 @@
         <x:v>2016</x:v>
       </x:c>
       <x:c r="G870" s="0" t="s">
-        <x:v>1672</x:v>
+        <x:v>2752</x:v>
       </x:c>
     </x:row>
     <x:row r="871">
@@ -33407,7 +33422,7 @@
         <x:v>2466</x:v>
       </x:c>
       <x:c r="G1086" s="0" t="s">
-        <x:v>2750</x:v>
+        <x:v>2753</x:v>
       </x:c>
     </x:row>
     <x:row r="1087">
@@ -33430,7 +33445,7 @@
         <x:v>2469</x:v>
       </x:c>
       <x:c r="G1087" s="0" t="s">
-        <x:v>2751</x:v>
+        <x:v>2754</x:v>
       </x:c>
     </x:row>
     <x:row r="1088">
@@ -33499,7 +33514,7 @@
         <x:v>2480</x:v>
       </x:c>
       <x:c r="G1090" s="0" t="s">
-        <x:v>2752</x:v>
+        <x:v>2755</x:v>
       </x:c>
     </x:row>
     <x:row r="1091">
@@ -33522,7 +33537,7 @@
         <x:v>2483</x:v>
       </x:c>
       <x:c r="G1091" s="0" t="s">
-        <x:v>2753</x:v>
+        <x:v>2756</x:v>
       </x:c>
     </x:row>
     <x:row r="1092">
@@ -33545,7 +33560,7 @@
         <x:v>2486</x:v>
       </x:c>
       <x:c r="G1092" s="0" t="s">
-        <x:v>2754</x:v>
+        <x:v>2757</x:v>
       </x:c>
     </x:row>
     <x:row r="1093">
@@ -33568,7 +33583,7 @@
         <x:v>2489</x:v>
       </x:c>
       <x:c r="G1093" s="0" t="s">
-        <x:v>2755</x:v>
+        <x:v>2758</x:v>
       </x:c>
     </x:row>
     <x:row r="1094">
@@ -33591,7 +33606,7 @@
         <x:v>2492</x:v>
       </x:c>
       <x:c r="G1094" s="0" t="s">
-        <x:v>1464</x:v>
+        <x:v>2759</x:v>
       </x:c>
     </x:row>
     <x:row r="1095">
@@ -33614,7 +33629,7 @@
         <x:v>2495</x:v>
       </x:c>
       <x:c r="G1095" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>2760</x:v>
       </x:c>
     </x:row>
     <x:row r="1096">
@@ -33637,7 +33652,7 @@
         <x:v>2498</x:v>
       </x:c>
       <x:c r="G1096" s="0" t="s">
-        <x:v>2756</x:v>
+        <x:v>2761</x:v>
       </x:c>
     </x:row>
     <x:row r="1097">
@@ -34488,7 +34503,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="G1133" s="0" t="s">
-        <x:v>2757</x:v>
+        <x:v>2762</x:v>
       </x:c>
     </x:row>
     <x:row r="1134">
@@ -34511,7 +34526,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="G1134" s="0" t="s">
-        <x:v>2757</x:v>
+        <x:v>2762</x:v>
       </x:c>
     </x:row>
     <x:row r="1135">
@@ -34534,7 +34549,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="G1135" s="0" t="s">
-        <x:v>2757</x:v>
+        <x:v>2762</x:v>
       </x:c>
     </x:row>
     <x:row r="1136">
@@ -34557,7 +34572,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="G1136" s="0" t="s">
-        <x:v>2757</x:v>
+        <x:v>2762</x:v>
       </x:c>
     </x:row>
     <x:row r="1137">
@@ -34580,7 +34595,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="G1137" s="0" t="s">
-        <x:v>2757</x:v>
+        <x:v>2762</x:v>
       </x:c>
     </x:row>
     <x:row r="1138">
@@ -34603,7 +34618,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="G1138" s="0" t="s">
-        <x:v>2757</x:v>
+        <x:v>2762</x:v>
       </x:c>
     </x:row>
     <x:row r="1139">
@@ -34626,7 +34641,7 @@
         <x:v>2588</x:v>
       </x:c>
       <x:c r="G1139" s="0" t="s">
-        <x:v>2757</x:v>
+        <x:v>2762</x:v>
       </x:c>
     </x:row>
     <x:row r="1140">
@@ -34649,7 +34664,7 @@
         <x:v>2603</x:v>
       </x:c>
       <x:c r="G1140" s="0" t="s">
-        <x:v>2758</x:v>
+        <x:v>2763</x:v>
       </x:c>
     </x:row>
     <x:row r="1141">
@@ -34672,7 +34687,7 @@
         <x:v>2603</x:v>
       </x:c>
       <x:c r="G1141" s="0" t="s">
-        <x:v>2758</x:v>
+        <x:v>2763</x:v>
       </x:c>
     </x:row>
     <x:row r="1142">
@@ -34695,7 +34710,7 @@
         <x:v>2603</x:v>
       </x:c>
       <x:c r="G1142" s="0" t="s">
-        <x:v>2758</x:v>
+        <x:v>2763</x:v>
       </x:c>
     </x:row>
     <x:row r="1143">
@@ -34718,7 +34733,7 @@
         <x:v>2610</x:v>
       </x:c>
       <x:c r="G1143" s="0" t="s">
-        <x:v>2759</x:v>
+        <x:v>2764</x:v>
       </x:c>
     </x:row>
     <x:row r="1144">
@@ -34741,7 +34756,7 @@
         <x:v>2613</x:v>
       </x:c>
       <x:c r="G1144" s="0" t="s">
-        <x:v>2760</x:v>
+        <x:v>2765</x:v>
       </x:c>
     </x:row>
     <x:row r="1145">
@@ -34764,7 +34779,7 @@
         <x:v>2613</x:v>
       </x:c>
       <x:c r="G1145" s="0" t="s">
-        <x:v>2760</x:v>
+        <x:v>2765</x:v>
       </x:c>
     </x:row>
     <x:row r="1146">
@@ -34787,7 +34802,7 @@
         <x:v>2613</x:v>
       </x:c>
       <x:c r="G1146" s="0" t="s">
-        <x:v>2760</x:v>
+        <x:v>2765</x:v>
       </x:c>
     </x:row>
     <x:row r="1147">
@@ -34810,7 +34825,7 @@
         <x:v>2613</x:v>
       </x:c>
       <x:c r="G1147" s="0" t="s">
-        <x:v>2760</x:v>
+        <x:v>2765</x:v>
       </x:c>
     </x:row>
     <x:row r="1148">
@@ -34833,7 +34848,7 @@
         <x:v>2622</x:v>
       </x:c>
       <x:c r="G1148" s="0" t="s">
-        <x:v>2761</x:v>
+        <x:v>2766</x:v>
       </x:c>
     </x:row>
     <x:row r="1149">
@@ -35109,7 +35124,7 @@
         <x:v>2655</x:v>
       </x:c>
       <x:c r="G1160" s="0" t="s">
-        <x:v>2762</x:v>
+        <x:v>2767</x:v>
       </x:c>
     </x:row>
     <x:row r="1161">
@@ -35132,7 +35147,7 @@
         <x:v>2658</x:v>
       </x:c>
       <x:c r="G1161" s="0" t="s">
-        <x:v>2763</x:v>
+        <x:v>2768</x:v>
       </x:c>
     </x:row>
     <x:row r="1162">
@@ -35155,7 +35170,7 @@
         <x:v>2661</x:v>
       </x:c>
       <x:c r="G1162" s="0" t="s">
-        <x:v>2764</x:v>
+        <x:v>2769</x:v>
       </x:c>
     </x:row>
     <x:row r="1163">
@@ -35178,7 +35193,7 @@
         <x:v>2664</x:v>
       </x:c>
       <x:c r="G1163" s="0" t="s">
-        <x:v>2765</x:v>
+        <x:v>2770</x:v>
       </x:c>
     </x:row>
     <x:row r="1164">
@@ -35201,7 +35216,7 @@
         <x:v>2667</x:v>
       </x:c>
       <x:c r="G1164" s="0" t="s">
-        <x:v>2766</x:v>
+        <x:v>2771</x:v>
       </x:c>
     </x:row>
     <x:row r="1165">
@@ -35224,7 +35239,7 @@
         <x:v>2670</x:v>
       </x:c>
       <x:c r="G1165" s="0" t="s">
-        <x:v>2767</x:v>
+        <x:v>2772</x:v>
       </x:c>
     </x:row>
     <x:row r="1166">
@@ -35339,7 +35354,7 @@
         <x:v>2682</x:v>
       </x:c>
       <x:c r="G1170" s="0" t="s">
-        <x:v>2768</x:v>
+        <x:v>2773</x:v>
       </x:c>
     </x:row>
     <x:row r="1171">
@@ -35362,7 +35377,7 @@
         <x:v>2685</x:v>
       </x:c>
       <x:c r="G1171" s="0" t="s">
-        <x:v>2769</x:v>
+        <x:v>2774</x:v>
       </x:c>
     </x:row>
     <x:row r="1172">
@@ -35385,7 +35400,7 @@
         <x:v>2688</x:v>
       </x:c>
       <x:c r="G1172" s="0" t="s">
-        <x:v>2770</x:v>
+        <x:v>2775</x:v>
       </x:c>
     </x:row>
     <x:row r="1173">
@@ -35408,7 +35423,7 @@
         <x:v>2691</x:v>
       </x:c>
       <x:c r="G1173" s="0" t="s">
-        <x:v>2771</x:v>
+        <x:v>2776</x:v>
       </x:c>
     </x:row>
     <x:row r="1174">
@@ -35431,7 +35446,7 @@
         <x:v>2694</x:v>
       </x:c>
       <x:c r="G1174" s="0" t="s">
-        <x:v>2772</x:v>
+        <x:v>2777</x:v>
       </x:c>
     </x:row>
     <x:row r="1175">
@@ -35454,7 +35469,7 @@
         <x:v>2697</x:v>
       </x:c>
       <x:c r="G1175" s="0" t="s">
-        <x:v>2773</x:v>
+        <x:v>2778</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
